--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221051</v>
+        <v>125221052</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664816</v>
+        <v>664815</v>
       </c>
       <c r="R2" t="n">
-        <v>7203648</v>
+        <v>7203647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221052</v>
+        <v>125221051</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664815</v>
+        <v>664816</v>
       </c>
       <c r="R3" t="n">
-        <v>7203647</v>
+        <v>7203648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221052</v>
+        <v>125221051</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664815</v>
+        <v>664816</v>
       </c>
       <c r="R2" t="n">
-        <v>7203647</v>
+        <v>7203648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221051</v>
+        <v>125221052</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664816</v>
+        <v>664815</v>
       </c>
       <c r="R3" t="n">
-        <v>7203648</v>
+        <v>7203647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221051</v>
+        <v>125221052</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664816</v>
+        <v>664815</v>
       </c>
       <c r="R2" t="n">
-        <v>7203648</v>
+        <v>7203647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221052</v>
+        <v>125221051</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664815</v>
+        <v>664816</v>
       </c>
       <c r="R3" t="n">
-        <v>7203647</v>
+        <v>7203648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221051</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221052</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221051</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221052</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221051</v>
       </c>
       <c r="B2" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221052</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22629-2025 artfynd.xlsx
+++ b/artfynd/A 22629-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221051</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221052</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
